--- a/questionnaire_templates/026_video_duration_preference_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/026_video_duration_preference_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'less_than_1_minute'}</t>
+          <t>less_than_1_minute</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'less than 1 minute'}</t>
+          <t>less than 1 minute</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'1-2_minutes'}</t>
+          <t>1-2_minutes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': '1-2 minutes'}</t>
+          <t>1-2 minutes</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'2-5_minutes'}</t>
+          <t>2-5_minutes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': '2-5 minutes'}</t>
+          <t>2-5 minutes</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'more_than_5_minutes'}</t>
+          <t>more_than_5_minutes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'more than 5 minutes'}</t>
+          <t>more than 5 minutes</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'youtube'}</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'YouTube'}</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'tiktok'}</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'TikTok'}</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_6,_'value':_'twitch'}</t>
+          <t>twitch</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 6, 'value': 'Twitch'}</t>
+          <t>Twitch</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_7,_'value':_'linkedin'}</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 7, 'value': 'LinkedIn'}</t>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_8,_'value':_'vimeo'}</t>
+          <t>vimeo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 8, 'value': 'Vimeo'}</t>
+          <t>Vimeo</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
